--- a/BOM/20211102 BOM TeKaDe UIBoard.xlsx
+++ b/BOM/20211102 BOM TeKaDe UIBoard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IngBuero\Projekte_Kunden\2021_TeKaDeRevival\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017708E-5C99-4489-AA6B-44CCDC69FB93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B110740-2A62-4333-B9BC-8AEC2A629F12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11960" xr2:uid="{261E8F2A-9F01-4E4B-AED6-14B6866C8B8C}"/>
   </bookViews>
@@ -796,15 +796,6 @@
     <t>696-SSL-LX5093LGD-TR</t>
   </si>
   <si>
-    <t>SSL-LX5093SRD/D</t>
-  </si>
-  <si>
-    <t>LED RD TINTED DIFF  60° 640nm</t>
-  </si>
-  <si>
-    <t>696-LX5093SRD/D</t>
-  </si>
-  <si>
     <t>210R/5%</t>
   </si>
   <si>
@@ -836,6 +827,15 @@
   </si>
   <si>
     <t>Available</t>
+  </si>
+  <si>
+    <t>SSL-LX5093LID</t>
+  </si>
+  <si>
+    <t>696-SSL-LX5093LID</t>
+  </si>
+  <si>
+    <t>LED RD TINTED DIFF  60° 635nm</t>
   </si>
 </sst>
 </file>
@@ -966,10 +966,10 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Erklärender Text" xfId="1" builtinId="53"/>
@@ -1310,15 +1310,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="21"/>
+      <c r="P1" s="22"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -1352,7 +1352,7 @@
         <v>217</v>
       </c>
       <c r="L2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
@@ -1399,7 +1399,7 @@
       <c r="K3" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="21">
         <v>58000</v>
       </c>
       <c r="M3" s="16">
@@ -1449,7 +1449,7 @@
       <c r="K4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="21">
         <v>20000</v>
       </c>
       <c r="M4" s="16">
@@ -1499,7 +1499,7 @@
       <c r="K5" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="21">
         <v>4600</v>
       </c>
       <c r="M5" s="16">
@@ -1525,31 +1525,31 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>194</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="21">
         <v>7400</v>
       </c>
       <c r="M6" s="16">
@@ -1575,16 +1575,16 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
         <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G7">
         <v>603</v>
@@ -1593,12 +1593,12 @@
         <v>225</v>
       </c>
       <c r="J7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K7" t="s">
         <v>218</v>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="21">
         <v>19000</v>
       </c>
       <c r="M7" s="18">
@@ -1645,7 +1645,7 @@
         <v>211</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="8" t="s">
@@ -1654,7 +1654,7 @@
       <c r="K9" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="21">
         <v>8800</v>
       </c>
       <c r="M9" s="10" t="s">
@@ -1687,7 +1687,7 @@
         <v>199</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="8" t="s">
@@ -1696,7 +1696,7 @@
       <c r="K10" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="21">
         <v>9000</v>
       </c>
       <c r="M10" s="10" t="s">
@@ -1741,7 +1741,7 @@
       <c r="K12" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="21">
         <v>1000</v>
       </c>
       <c r="M12" s="16">
@@ -1820,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1829,33 +1829,33 @@
         <v>247</v>
       </c>
       <c r="F15" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="G15" t="s">
         <v>245</v>
       </c>
       <c r="J15" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="K15" t="s">
         <v>218</v>
       </c>
-      <c r="L15" s="22">
-        <v>57000</v>
+      <c r="L15" s="21">
+        <v>4800</v>
       </c>
       <c r="M15" s="18">
-        <v>0.20899999999999999</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="N15" s="18">
-        <v>9.2999999999999999E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="O15" s="18">
         <f>B15*M15</f>
-        <v>0.20899999999999999</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="P15" s="18">
         <f>N15*B15</f>
-        <v>9.2999999999999999E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -1886,7 +1886,7 @@
       <c r="K16" t="s">
         <v>218</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="21">
         <v>2100</v>
       </c>
       <c r="M16" s="18">
@@ -1932,7 +1932,7 @@
       <c r="K17" t="s">
         <v>218</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="21">
         <v>9300</v>
       </c>
       <c r="M17" s="18">
@@ -1978,7 +1978,7 @@
       <c r="K18" t="s">
         <v>218</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="21">
         <v>2400</v>
       </c>
       <c r="M18" s="18">
@@ -2024,7 +2024,7 @@
       <c r="K19" t="s">
         <v>235</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="21">
         <v>12400</v>
       </c>
       <c r="M19" s="18">
@@ -2076,7 +2076,7 @@
       <c r="K21" t="s">
         <v>218</v>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="21">
         <v>2700</v>
       </c>
       <c r="M21" s="18">
@@ -2122,7 +2122,7 @@
       <c r="K22" t="s">
         <v>218</v>
       </c>
-      <c r="L22" s="22">
+      <c r="L22" s="21">
         <v>36</v>
       </c>
       <c r="M22" s="18">
